--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Servizi idrici.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Servizi idrici.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="151">
   <si>
     <r>
       <t xml:space="preserve">
@@ -1246,7 +1246,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è stata accolta. 
+      <t xml:space="preserve"> è stata accolta.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -1274,7 +1274,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> non è stata accolta. 
+      <t xml:space="preserve"> non è stata accolta.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -1746,13 +1746,16 @@
     </r>
   </si>
   <si>
-    <t>Completa richiesta</t>
+    <t>Completa la richiesta</t>
   </si>
   <si>
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>Accedi al portale</t>
   </si>
   <si>
     <r>
@@ -1772,7 +1775,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1888,14 +1891,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -2771,7 +2766,7 @@
         <v>118</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I6" s="34" t="s">
         <v>117</v>
@@ -2806,7 +2801,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>66</v>
@@ -2862,7 +2857,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>118</v>
@@ -2918,119 +2913,119 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>122</v>
-      </c>
       <c r="E9" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G9" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="H9" s="34" t="s">
-        <v>122</v>
-      </c>
       <c r="I9" s="34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q9" s="34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R9" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" s="34" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P10" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q10" s="34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R10" s="34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>66</v>
@@ -3042,10 +3037,10 @@
         <v>66</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>66</v>
@@ -3054,10 +3049,10 @@
         <v>66</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="K11" s="34" t="s">
         <v>66</v>
@@ -3066,16 +3061,16 @@
         <v>66</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="N11" s="34" t="s">
         <v>66</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q11" s="34" t="s">
         <v>66</v>
